--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9197-2023 artfynd.xlsx
+++ b/artfynd/A 9197-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131597494</v>
       </c>
       <c r="B2" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
